--- a/rules/CORE-000744/positive/02/data/unit-test-coreid-CG0174_positive.AEFA_SEQ.xlsx
+++ b/rules/CORE-000744/positive/02/data/unit-test-coreid-CG0174_positive.AEFA_SEQ.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1199,6 +1199,94 @@
         </is>
       </c>
       <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GUARD-FAOBJ</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SORE HEAD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Headache</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nervous system disorders</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SEVERE</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NOT APPLICABLE</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>DEFINITELY NOT RELATED</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>RECOVERED/RESOLVED</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2022-03-19</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2022-03-19</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1211,7 +1299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1792,6 +1880,77 @@
       </c>
       <c r="P8" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GUARD-FAOBJ</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OCCUR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Occurrence Indicator</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Headache</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ERYTHEMA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2012-12-02</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1805,7 +1964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2054,6 +2213,66 @@
         <v>2</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GUARD-FAOBJ</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AESEQ</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GUARD-FAOBJ</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FASEQ</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>G1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
